--- a/output/Reims_Polar_2026.xlsx
+++ b/output/Reims_Polar_2026.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Séances" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Séances'!$A$1:$G$140</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -415,87 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Catégorie</t>
+          <t>film</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Film</t>
+          <t>categorie</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Durée</t>
+          <t>duree</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>duree_minutes</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Jour</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Heure</t>
+          <t>jour</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Salle</t>
+          <t>heure</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>salle</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>LA CORDE AU COU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>GVS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LA CORDE AU COU</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>1h44</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>104</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Mar 31</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>19h00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -504,35 +501,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>LA CORDE AU COU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>GVS</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LA CORDE AU COU</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>1h44</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Mar 31</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -541,109 +541,108 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SEVEN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2h07</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>SPÉ CHICAGO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10h00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Salle 11</t>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CORSE</t>
+          <t>SEVEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BORGO</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1h57</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2h07</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>127</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>10h00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Salle 11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>R ED CODE BLUE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>R ED CODE BLUE</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>2h28</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>148</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>10h30</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -652,179 +651,198 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>LE BOUCHER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDOMPTABLES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1h21</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>1h30</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>M LE MAUDIT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LE BOUCHER</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1h58</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>118</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>L’AFFAIRE SK1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>M LE MAUDIT</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1h58</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2h00</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>INDOMPTABLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L’AFFAIRE SK1</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2h00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>1h21</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>81</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>LE MAURE DE KARATAS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LE MAURE DE KARATAS</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>1h23</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>83</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>14h30</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -833,12 +851,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>PARANOID PARK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G ROWING DOWN</t>
+          <t>GVS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -846,203 +864,225 @@
           <t>1h25</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GVS</t>
+          <t>LES MISÉRABLES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PARANOID PARK</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+          <t>FOCUS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1h45</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>105</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>LES CHAMBRES ROUGES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LES MISÉRABLES</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1h45</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>1h58</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>118</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>U NE PLUIE SANS FIN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LES CHAMBRES ROUGES</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1h58</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>1h59</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>119</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>G ROWING DOWN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U NE PLUIE SANS FIN</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1h59</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>1h25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>85</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SHAM</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>2h09</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>129</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>16h30</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -1051,35 +1091,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>LE MAURE DE KARATAS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LE MAURE DE KARATAS</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>1h23</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>83</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -1088,31 +1131,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>SEULES LES BÊTES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>FOCUS</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SEULES LES BÊTES</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1h57</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>117</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -1121,35 +1171,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>DE GRANDES ESPÉRANCES</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DE GRANDES ESPÉRANCES</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>1h45</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>105</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -1158,35 +1211,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>PULSIONS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PULSIONS</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>1h45</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>105</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -1195,35 +1251,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>TÉNÈBRES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TÉNÈBRES</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>1h41</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>101</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -1232,35 +1291,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>LE CRI DES GARDES</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>LE CRI DES GARDES</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>1h49</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>109</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>19h30</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -1269,35 +1331,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>LE CRI DES GARDES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LE CRI DES GARDES</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>1h49</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>109</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -1306,35 +1371,38 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>R ED CODE BLUE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R ED CODE BLUE</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>2h28</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>148</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -1343,35 +1411,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>G ROWING DOWN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>G ROWING DOWN</t>
-        </is>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>1h25</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>85</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -1380,35 +1451,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>MEMORIES OF MURDER</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MEMORIES OF MURDER</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>2h11</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>131</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -1417,35 +1491,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>LES CRIMES DE SNOWTOWN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LES CRIMES DE SNOWTOWN</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>2h00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>120</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -1454,35 +1531,38 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SHAM</t>
-        </is>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>2h09</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>129</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Mer 1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -1491,31 +1571,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>PRÊTE À TOUT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>GVS</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PRÊTE À TOUT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1h46</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>106</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>10h00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -1524,35 +1611,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>DISASTER</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>DISASTER</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>2h08</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>128</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>10h30</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -1561,216 +1651,238 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>LE SIXIÈME SENS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FATHER</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1h43</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2h00</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>120</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>LE MAURE DE KARATAS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LE SIXIÈME SENS</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1h23</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>83</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>LES CRIMES DE SNOWTOWN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LE MAURE DE KARATAS</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1h23</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2h00</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>120</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SHAM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LES CRIMES DE SNOWTOWN</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2h00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2h09</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>129</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>FATHER</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHAM</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2h09</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>1h43</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>103</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>R ED CODE BLUE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>R ED CODE BLUE</t>
-        </is>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>2h28</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>148</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -1779,35 +1891,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>K EEP QUIET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>K EEP QUIET</t>
-        </is>
-      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>1h44</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>104</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>14h30</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -1816,35 +1931,38 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>ELEPHANT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>GVS</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ELEPHANT</t>
-        </is>
-      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>1h21</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>81</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -1853,35 +1971,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>LES FORTS NE DISENT RIEN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>LES FORTS NE DISENT RIEN</t>
-        </is>
-      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>32 min</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>32</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -1890,31 +2011,38 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>NUIT BLEUE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NUIT BLEUE</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1h26</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>86</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -1923,35 +2051,38 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>S IX FEMMES POUR L’ASSASSIN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>S IX FEMMES POUR L’ASSASSIN</t>
-        </is>
-      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>1h28</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>88</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -1960,35 +2091,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>GRAND CIEL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>FOCUS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>GRAND CIEL</t>
-        </is>
-      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>1h31</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>91</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -1997,35 +2131,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>T HE LAST VIKING</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>T HE LAST VIKING</t>
-        </is>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>116</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>16h45</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -2034,35 +2171,38 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>MORTE CUCINA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>MORTE CUCINA</t>
-        </is>
-      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>1h36</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>96</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -2071,35 +2211,38 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>DISASTER</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>DISASTER</t>
-        </is>
-      </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>2h08</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>128</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -2108,35 +2251,38 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>G ROWING DOWN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>G ROWING DOWN</t>
-        </is>
-      </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>1h25</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>85</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -2145,35 +2291,38 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>INDOMPTABLES</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>PCC</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>INDOMPTABLES</t>
-        </is>
-      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>1h21</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>81</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -2182,35 +2331,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>LE CRI DES GARDES</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LE CRI DES GARDES</t>
-        </is>
-      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>1h49</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>109</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -2219,35 +2371,38 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>FATHER</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>FATHER</t>
-        </is>
-      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>1h43</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>103</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -2256,35 +2411,38 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>MI AMOR</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MI AMOR</t>
-        </is>
-      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>1h55</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>115</v>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>19h30</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -2293,35 +2451,38 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>MI AMOR</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MI AMOR</t>
-        </is>
-      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>1h55</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>115</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -2330,35 +2491,38 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>T HE LAST VIKING</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>T HE LAST VIKING</t>
-        </is>
-      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>116</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -2367,35 +2531,38 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>MORTE CUCINA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MORTE CUCINA</t>
-        </is>
-      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>1h36</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>96</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -2404,35 +2571,38 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>K EEP QUIET</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>K EEP QUIET</t>
-        </is>
-      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>1h44</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>104</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -2441,35 +2611,38 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>LE CRI DES GARDES</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LE CRI DES GARDES</t>
-        </is>
-      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>1h49</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>109</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -2478,35 +2651,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>FATHER</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FATHER</t>
-        </is>
-      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>1h43</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>103</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Jeu 2</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -2515,35 +2691,38 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>INDOMPTABLES</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>PCC</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>INDOMPTABLES</t>
-        </is>
-      </c>
       <c r="C58" t="inlineStr">
         <is>
           <t>1h21</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>81</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>10h00</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -2552,35 +2731,38 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>G AGNE TON CIEL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>G AGNE TON CIEL</t>
-        </is>
-      </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>116</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>10h30</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -2589,68 +2771,78 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>DIQUÀ DAI MONTI, EN-DEÇÀ-DES-MONTS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SOVEREIGN</t>
+          <t>CORSE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1h40</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>27 min</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>27</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>LE MOHICAN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>DIQUÀ DAI MONTI, EN-DEÇÀ-DES-MONTS</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1h27</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>87</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -2659,175 +2851,198 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CORSE</t>
+          <t>MORTE CUCINA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LE MOHICAN</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
+          <t>SANG</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1h36</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>96</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>R ED CODE BLUE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MORTE CUCINA</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1h36</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2h28</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>148</v>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>GRAND CIEL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R ED CODE BLUE</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2h28</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>1h31</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>91</v>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>SOVEREIGN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GRAND CIEL</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1h31</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>1h40</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>LE BOUCHER</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>LE BOUCHER</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1h30</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>90</v>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -2836,35 +3051,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>LES SILENCES DE RIYAD</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>LES SILENCES DE RIYAD</t>
-        </is>
-      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>1h39</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>99</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>14h30</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -2873,68 +3091,78 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>LE JOUR DE MA MORT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SISTER</t>
+          <t>CORSE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1h27</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>19 min</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>19</v>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>LES APACHES</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>LE JOUR DE MA MORT</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1h22</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>82</v>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -2943,179 +3171,198 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CORSE</t>
+          <t>G ROWING DOWN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LES APACHES</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
+          <t>SANG</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1h25</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>85</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>K EEP QUIET</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>G ROWING DOWN</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1h25</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>1h44</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>104</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>G AGNE TON CIEL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>K EEP QUIET</t>
-        </is>
-      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1h44</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>1h56</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>116</v>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>SISTER</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>G AGNE TON CIEL</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1h56</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>1h27</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>87</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>THE CRIMINALS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>THE CRIMINALS</t>
-        </is>
-      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>1h38</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="n">
+        <v>98</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -3124,64 +3371,78 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SÉRIE</t>
+          <t>LA NUIT EST LÀ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U NTIL I KILL YOU</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
+          <t>CORSE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>25 min</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>LE SILENCE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>LA NUIT EST LÀ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1h44</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>104</v>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -3190,179 +3451,198 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CORSE</t>
+          <t>SOVEREIGN</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LE SILENCE</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr">
+          <t>SANG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1h40</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>100</v>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>K EEP QUIET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOVEREIGN</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1h40</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>1h44</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>104</v>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>LES SILENCES DE RIYAD</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>K EEP QUIET</t>
-        </is>
-      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1h44</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>1h39</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>99</v>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>U NTIL I KILL YOU</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LES SILENCES DE RIYAD</t>
+          <t>SÉRIE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1h39</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>1h30</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>90</v>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>W INTER OF THE CROW</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>W INTER OF THE CROW</t>
-        </is>
-      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>1h52</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="n">
+        <v>112</v>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>19h30</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -3371,257 +3651,278 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>SISTER</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>W INTER OF THE CROW</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1h52</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>1h27</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>87</v>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>THE CRIMINALS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>G AGNE TON CIEL</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1h56</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>1h38</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>98</v>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Salle 11</t>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>SISTER</t>
-        </is>
-      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1h27</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>1h40</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>100</v>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>FATHER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>THE CRIMINALS</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1h38</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>1h43</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>103</v>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>W INTER OF THE CROW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SOVEREIGN</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1h40</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>1h52</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>112</v>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>G AGNE TON CIEL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FATHER</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1h43</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>1h56</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>116</v>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Salle 11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>DISASTER</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DISASTER</t>
-        </is>
-      </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>2h08</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="n">
+        <v>128</v>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -3630,35 +3931,38 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>G ROWING DOWN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>G ROWING DOWN</t>
-        </is>
-      </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>1h25</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="n">
+        <v>85</v>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -3667,35 +3971,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>MORTE CUCINA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>MORTE CUCINA</t>
-        </is>
-      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>1h36</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="n">
+        <v>96</v>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -3704,35 +4011,38 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>G AGNE TON CIEL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>G AGNE TON CIEL</t>
-        </is>
-      </c>
       <c r="C91" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>116</v>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -3741,35 +4051,38 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>MI AMOR</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>MI AMOR</t>
-        </is>
-      </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>1h55</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="n">
+        <v>115</v>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Ven 3</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>22h15</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -3778,35 +4091,38 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>S ONS OF THE NEON NIGHT</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>S ONS OF THE NEON NIGHT</t>
-        </is>
-      </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>2h05</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="n">
+        <v>125</v>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>10h30</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -3815,160 +4131,172 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>BORGO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S OUS EMPRISE</t>
+          <t>CORSE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1h56</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>1h57</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>117</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CORSE</t>
+          <t>SISTER</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BORGO</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1h57</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>1h27</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>87</v>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>K EEP QUIET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SISTER</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1h27</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>1h44</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>104</v>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>G AGNE TON CIEL</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>K EEP QUIET</t>
-        </is>
-      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1h44</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>1h56</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>116</v>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>S OUS EMPRISE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>G AGNE TON CIEL</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3976,59 +4304,65 @@
           <t>1h56</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="n">
+        <v>116</v>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>SOVEREIGN</t>
-        </is>
-      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>1h40</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="n">
+        <v>100</v>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>11h30</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -4037,183 +4371,198 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>S OUS EMPRISE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S ONS OF THE NEON NIGHT</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2h05</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>1h56</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>116</v>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>R ED CODE BLUE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S OUS EMPRISE</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1h56</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+          <t>2h28</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>148</v>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>MI AMOR</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>R ED CODE BLUE</t>
-        </is>
-      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2h28</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>1h55</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>115</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>S ONS OF THE NEON NIGHT</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>MI AMOR</t>
-        </is>
-      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1h55</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2h05</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>125</v>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>14h00</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>LE MAURE DE KARATAS</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>LE MAURE DE KARATAS</t>
-        </is>
-      </c>
       <c r="C104" t="inlineStr">
         <is>
           <t>1h23</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="n">
+        <v>83</v>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>14h30</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -4222,72 +4571,78 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SÉRIE</t>
+          <t>CHIENS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PAOLO</t>
+          <t>CORSE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1h48</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>24 min</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>24</v>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>LE ROYAUME</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>CORSE</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CHIENS</t>
-        </is>
-      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>24 min</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+          <t>1h51</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>111</v>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -4296,179 +4651,198 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CORSE</t>
+          <t>DISASTER</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LE ROYAUME</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2h08</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>128</v>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>W INTER OF THE CROW</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>DISASTER</t>
-        </is>
-      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2h08</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>1h52</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>112</v>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>LES SILENCES DE RIYAD</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>W INTER OF THE CROW</t>
-        </is>
-      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1h52</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+          <t>1h39</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>99</v>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>PAOLO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LES SILENCES DE RIYAD</t>
+          <t>SÉRIE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1h39</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>1h48</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>108</v>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>T HE LAST VIKING</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>T HE LAST VIKING</t>
-        </is>
-      </c>
       <c r="C111" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" t="n">
+        <v>116</v>
+      </c>
+      <c r="E111" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -4477,35 +4851,38 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>MATA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>MATA</t>
-        </is>
-      </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>1h35</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="n">
+        <v>95</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>19h30</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -4514,179 +4891,198 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>THE CRIMINALS</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>MATA</t>
-        </is>
-      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1h35</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+          <t>1h38</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>98</v>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>LES MISÉRABLES</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>T HE LAST VIKING</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1h56</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+          <t>1h45</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>105</v>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Salle 11</t>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>MATA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>THE CRIMINALS</t>
-        </is>
-      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1h38</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+          <t>1h35</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>95</v>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>T HE LAST VIKING</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LES MISÉRABLES</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1h45</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>1h56</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>116</v>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>20h00</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Salle 11</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>J’AI RENCONTRÉ LE DIABLE</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>J’AI RENCONTRÉ LE DIABLE</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2h22</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>142</v>
+      </c>
+      <c r="E117" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -4695,35 +5091,38 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SHAM</t>
-        </is>
-      </c>
       <c r="C118" t="inlineStr">
         <is>
           <t>2h09</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="n">
+        <v>129</v>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>20h30</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -4732,146 +5131,158 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>THE CRIMINALS</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>MATA</t>
-        </is>
-      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1h35</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+          <t>1h38</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>98</v>
+      </c>
+      <c r="E119" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>W INTER OF THE CROW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>THE CRIMINALS</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1h38</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+          <t>1h52</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>112</v>
+      </c>
+      <c r="E120" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>W INTER OF THE CROW</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1h52</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+          <t>1h35</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>95</v>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>22h00</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>LES SILENCES DE RIYAD</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>LES SILENCES DE RIYAD</t>
-        </is>
-      </c>
       <c r="C122" t="inlineStr">
         <is>
           <t>1h39</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" t="n">
+        <v>99</v>
+      </c>
+      <c r="E122" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Sam 4</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>22h15</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -4880,257 +5291,274 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DISASTER</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U NE PLUIE SANS FIN</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1h59</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2h08</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>128</v>
+      </c>
+      <c r="E123" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Salle 10</t>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Salle 4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>LE MAURE DE KARATAS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>LES SILENCES DE RIYAD</t>
-        </is>
-      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1h39</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+          <t>1h23</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>83</v>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Salle 11</t>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Salle 7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>W INTER OF THE CROW</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>DISASTER</t>
-        </is>
-      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2h08</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+          <t>1h52</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>112</v>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Salle 4</t>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>MI AMOR</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>LE MAURE DE KARATAS</t>
-        </is>
-      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>1h23</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>1h55</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>115</v>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Salle 7</t>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>COMP</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>W INTER OF THE CROW</t>
-        </is>
-      </c>
+          <t>SPÉ U NE VIE DE CHAT</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1h52</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+          <t>1h10</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>70</v>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>LES SILENCES DE RIYAD</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>COMP</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>MI AMOR</t>
-        </is>
-      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1h55</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+          <t>1h39</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>99</v>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>11h00</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Salle 9</t>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Salle 11</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>MATA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>MATA</t>
-        </is>
-      </c>
       <c r="C129" t="inlineStr">
         <is>
           <t>1h35</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="n">
+        <v>95</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>14h30</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -5139,35 +5567,38 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>T HE LAST VIKING</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>T HE LAST VIKING</t>
-        </is>
-      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="n">
+        <v>116</v>
+      </c>
+      <c r="E130" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>14h30</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
@@ -5176,35 +5607,38 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>SISTER</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>SISTER</t>
-        </is>
-      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>1h27</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" t="n">
+        <v>87</v>
+      </c>
+      <c r="E131" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -5213,35 +5647,38 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>S OUS EMPRISE</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>S OUS EMPRISE</t>
-        </is>
-      </c>
       <c r="C132" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" t="n">
+        <v>116</v>
+      </c>
+      <c r="E132" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -5250,35 +5687,38 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>SOVEREIGN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>SOVEREIGN</t>
-        </is>
-      </c>
       <c r="C133" t="inlineStr">
         <is>
           <t>1h40</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="n">
+        <v>100</v>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -5287,35 +5727,38 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>FATHER</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>FATHER</t>
-        </is>
-      </c>
       <c r="C134" t="inlineStr">
         <is>
           <t>1h43</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="n">
+        <v>103</v>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>15h00</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -5324,35 +5767,38 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>SISTER</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>SISTER</t>
-        </is>
-      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>1h27</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="n">
+        <v>87</v>
+      </c>
+      <c r="E135" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -5361,35 +5807,38 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>MORTE CUCINA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>MORTE CUCINA</t>
-        </is>
-      </c>
       <c r="C136" t="inlineStr">
         <is>
           <t>1h36</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" t="n">
+        <v>96</v>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>Salle 8</t>
         </is>
@@ -5398,35 +5847,38 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>SHAM</t>
-        </is>
-      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>2h09</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" t="n">
+        <v>129</v>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>17h00</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>Salle 9</t>
         </is>
@@ -5435,35 +5887,38 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>S OUS EMPRISE</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>SANG</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>S OUS EMPRISE</t>
-        </is>
-      </c>
       <c r="C138" t="inlineStr">
         <is>
           <t>1h56</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" t="n">
+        <v>116</v>
+      </c>
+      <c r="E138" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>17h15</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -5472,35 +5927,38 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>THE CRIMINALS</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>AVP</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>THE CRIMINALS</t>
-        </is>
-      </c>
       <c r="C139" t="inlineStr">
         <is>
           <t>1h38</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" t="n">
+        <v>98</v>
+      </c>
+      <c r="E139" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>Salle 10</t>
         </is>
@@ -5509,42 +5967,44 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>INDOMPTABLES</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>PCC</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>INDOMPTABLES</t>
-        </is>
-      </c>
       <c r="C140" t="inlineStr">
         <is>
           <t>1h21</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" t="n">
+        <v>81</v>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Dim 5</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>17h30</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>Salle 11</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>